--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_65318_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_65318_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbb7435359e9e4b19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R84a76992d4364f8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7083</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4496</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3688</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_65318_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_65318_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R84a76992d4364f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4b1cb13330754f77"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5004</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6533</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4546</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4379</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4625</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7929</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0657</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5263</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5842</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4373</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4967</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4879</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6171</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4921</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9079</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9417</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3692</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4279</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4935</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6813</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4421</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3942</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3052</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3255</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3029</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3279</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3454</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7946</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5029</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3979</x:v>
+        <x:v>      1.4079</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4725</x:v>
+        <x:v>      1.4825</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7083</x:v>
+        <x:v>      1.7183</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.5450</x:v>
+        <x:v>      1.5550</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4679</x:v>
+        <x:v>      1.4779</x:v>
       </x:c>
     </x:row>
     <x:row>
